--- a/medical_surveys_questionnaires/044_covid_contact_tracing_form_template--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/044_covid_contact_tracing_form_template--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In-person', 'value': 'in-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_active',_'value':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Active', 'value': 'not_active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not Completed', 'value': 'not_completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
